--- a/data/inputs/reglas_local.xlsx
+++ b/data/inputs/reglas_local.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaimeteran/Documents/PYTHON/vacanze_romane/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaimeteran/Documents/PYTHON/VacanzeGIT/data/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ADBCD4A-4509-1F40-8080-EAE6BF3233D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1242FBC5-874B-C94C-9759-AC943F41E36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" xr2:uid="{0CB8002A-4321-7447-B7A9-BC49A85ACC14}"/>
   </bookViews>
@@ -528,5 +528,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
--- a/data/inputs/reglas_local.xlsx
+++ b/data/inputs/reglas_local.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaimeteran/Documents/PYTHON/VacanzeGIT/data/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1242FBC5-874B-C94C-9759-AC943F41E36B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39DDCD9-5456-984A-8D23-13D4DC696DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" xr2:uid="{0CB8002A-4321-7447-B7A9-BC49A85ACC14}"/>
   </bookViews>

--- a/data/inputs/reglas_local.xlsx
+++ b/data/inputs/reglas_local.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jaimeteran/Documents/PYTHON/VacanzeGIT/data/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E39DDCD9-5456-984A-8D23-13D4DC696DB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A645528-EC4C-4F4A-8F25-A2587BDE4D81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="17160" xr2:uid="{0CB8002A-4321-7447-B7A9-BC49A85ACC14}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>parametro</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>descanso_entre_turnos</t>
+  </si>
+  <si>
+    <t>##2##</t>
   </si>
 </sst>
 </file>
@@ -440,13 +443,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D0A0157-AE5F-6C48-87B2-0A1AF3A5AB54}">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="21.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -454,7 +457,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -462,7 +465,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -470,7 +473,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -478,15 +481,18 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>5</v>
       </c>
       <c r="B5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -494,7 +500,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -502,7 +508,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>8</v>
       </c>
@@ -510,7 +516,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -518,7 +524,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>10</v>
       </c>
